--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N89_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N89_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>11.11896529936669</v>
+        <v>1.806831861147086</v>
       </c>
       <c r="D2" t="n">
-        <v>10.85111261191542</v>
+        <v>1.763305799436256</v>
       </c>
       <c r="E2" t="n">
-        <v>17.3238239232831</v>
+        <v>2.815121387533504</v>
       </c>
       <c r="F2" t="n">
-        <v>3.482930916030174</v>
+        <v>0.5659762738549032</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.76661314593289</v>
+        <v>7.437074636214096</v>
       </c>
       <c r="D3" t="n">
-        <v>17.81697444397577</v>
+        <v>2.895258347146063</v>
       </c>
       <c r="E3" t="n">
-        <v>17.3238239232831</v>
+        <v>2.815121387533504</v>
       </c>
       <c r="F3" t="n">
-        <v>3.482930916030174</v>
+        <v>0.5659762738549032</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
